--- a/source/09_GenerativeAI_RPA/genai_rpa.xlsx
+++ b/source/09_GenerativeAI_RPA/genai_rpa.xlsx
@@ -1,24 +1,24 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28827"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\ai_x\source\09_GenerativeAI_RPA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BAA8EE63-9240-4D2F-8FA9-BFB0A425DBED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B0A37126-E319-400D-AFC5-7F50B8C5684B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-23148" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2970" yWindow="165" windowWidth="24600" windowHeight="9210" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="origin_report" sheetId="26" r:id="rId1"/>
-    <sheet name="prev_report" sheetId="202" r:id="rId2"/>
-    <sheet name="now_report" sheetId="205" r:id="rId3"/>
+    <sheet name="now_report" sheetId="205" r:id="rId2"/>
+    <sheet name="prev_report" sheetId="209" r:id="rId3"/>
     <sheet name="now_report_en" sheetId="206" r:id="rId4"/>
     <sheet name="now_list" sheetId="204" r:id="rId5"/>
-    <sheet name="prev_list" sheetId="207" r:id="rId6"/>
+    <sheet name="prev_list" sheetId="208" r:id="rId6"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="379" uniqueCount="230">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="309" uniqueCount="239">
   <si>
     <t>OOO 일일 동향 보고서</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -89,12 +89,6 @@
     <t>category4</t>
   </si>
   <si>
-    <t>쿠팡</t>
-  </si>
-  <si>
-    <t>옥션</t>
-  </si>
-  <si>
     <t>생활/건강</t>
   </si>
   <si>
@@ -104,311 +98,16 @@
     <t>미용/목욕</t>
   </si>
   <si>
-    <t>샴푸/린스/비누</t>
-  </si>
-  <si>
-    <t>개 대 정장 샴푸 프레스 대비누대 비누 블랙 치솔 칫솔 세트 플라스틱 욕실 치솔꽂이</t>
-  </si>
-  <si>
-    <t>https://link.auction.co.kr/gate/pcs?item-no=E946603010&amp;sub-id=1&amp;service-code=10000003</t>
-  </si>
-  <si>
-    <t>https://shopping-phinf.pstatic.net/main_5385874/53858743882.jpg</t>
-  </si>
-  <si>
-    <t>욕실용품</t>
-  </si>
-  <si>
-    <t>욕실용기/홀더</t>
-  </si>
-  <si>
-    <t>비눗갑/홀더/받침</t>
-  </si>
-  <si>
-    <t>시리우스 강아지 발씻자 270mlx3+실리콘팁</t>
-  </si>
-  <si>
-    <t>https://smartstore.naver.com/main/products/11655509301</t>
-  </si>
-  <si>
-    <t>https://shopping-phinf.pstatic.net/main_8920001/89200019767.jpg</t>
-  </si>
-  <si>
-    <t>노마타운</t>
-  </si>
-  <si>
-    <t>시리우스</t>
-  </si>
-  <si>
     <t>기타반려동물용품</t>
   </si>
   <si>
-    <t>오구비포</t>
-  </si>
-  <si>
-    <t>가려운 피부를 위한 오트밀 개 샴푸 건조한 각질 민감성 피부 알레르기 및 가려움증을 목욕 비누</t>
-  </si>
-  <si>
-    <t>https://smartstore.naver.com/main/products/11655458215</t>
-  </si>
-  <si>
-    <t>https://shopping-phinf.pstatic.net/main_8919996/89199968681.jpg</t>
-  </si>
-  <si>
-    <t>(2세트할인) 미국 크라운로얄 바이오바이트 컨디션플러스 말티즈 꼬똥 시츄 아프간  3단모파상모이중모테리어  2개  236ml</t>
-  </si>
-  <si>
-    <t>https://link.coupang.com/re/PCSNAVERPCSDP?pageKey=7657698009&amp;ctag=7657698009&amp;lptag=V82570136419&amp;itemId=20392616548&amp;vendorItemId=82570136419&amp;spec=10305199</t>
-  </si>
-  <si>
-    <t>https://shopping-phinf.pstatic.net/main_5385865/53858651732.jpg</t>
-  </si>
-  <si>
-    <t>스퀘어 화이트 크래프트 블랙 포장 상자 웨딩 파티 개 수제 용품 비누 선물 평면 초콜릿 10</t>
-  </si>
-  <si>
-    <t>https://link.auction.co.kr/gate/pcs?item-no=E946586220&amp;sub-id=1&amp;service-code=10000003</t>
-  </si>
-  <si>
-    <t>https://shopping-phinf.pstatic.net/main_5385873/53858734010.jpg</t>
-  </si>
-  <si>
-    <t>공구</t>
-  </si>
-  <si>
-    <t>포장용품</t>
-  </si>
-  <si>
-    <t>선물박스</t>
-  </si>
-  <si>
-    <t>블랙 크래프트 골판지 상자 선물 공예 놀이 명함 9.2 50 종이 차 비누 개/로트 포장 5.5 4cm</t>
-  </si>
-  <si>
-    <t>https://link.auction.co.kr/gate/pcs?item-no=E946580254&amp;sub-id=1&amp;service-code=10000003</t>
-  </si>
-  <si>
-    <t>https://shopping-phinf.pstatic.net/main_5385872/53858727893.jpg</t>
-  </si>
-  <si>
-    <t>화방용품</t>
-  </si>
-  <si>
-    <t>전문지류/미술지류</t>
-  </si>
-  <si>
-    <t>골판지</t>
-  </si>
-  <si>
-    <t>욕조에 있는 사랑스러운 프렌치 불독 캔버스 벽 예술 인쇄, 12x18인치 - 액자 없는 현대적인 욕실 장식과 비누 디스펜서, 집이나 방 장식을 위한 재미있는 개 일러스트레이션,</t>
-  </si>
-  <si>
-    <t>https://temuaffiliateprogram.pxf.io/c/5257454/1580294/18350?u=https%3A%2F%2Fwww.temu.com%2Fkr%2Fgoods.html%3Fsku_id%3D17594869875357%26goods_id%3D601100132138879%26_x_ns_catalog_id%3D10000%26_x_ns_product_id%3D17594869875357%26_x_ns_site_id%3D119%26_x_ns_ad%3d{ad}</t>
-  </si>
-  <si>
-    <t>https://shopping-phinf.pstatic.net/main_5385872/53858722011.jpg</t>
-  </si>
-  <si>
-    <t>TEMU kr</t>
-  </si>
-  <si>
-    <t>가구/인테리어</t>
-  </si>
-  <si>
-    <t>인테리어소품</t>
-  </si>
-  <si>
-    <t>액자</t>
-  </si>
-  <si>
-    <t>퍼즐/그림/사진액자</t>
-  </si>
-  <si>
-    <t>창문형 미니 크래프트 종이 상자 포장 비누 베이커리 블랙 화이트 브라운 개 30</t>
-  </si>
-  <si>
-    <t>https://link.auction.co.kr/gate/pcs?item-no=E946621381&amp;sub-id=1&amp;service-code=10000003</t>
-  </si>
-  <si>
-    <t>https://shopping-phinf.pstatic.net/main_5385869/53858696356.jpg</t>
-  </si>
-  <si>
-    <t>외부 금속 사인 웨스티용 장식 강아지 목욕 비누 회사 재미있는 욕실 빈티지 홈 소박한 알루미늄  1개  2. 20x30cm</t>
-  </si>
-  <si>
-    <t>https://link.coupang.com/re/PCSNAVERPCSDP?pageKey=8684133347&amp;ctag=8684133347&amp;lptag=P8684133347&amp;itemId=25159103573&amp;vendorItemId=92157151447&amp;spec=10305199</t>
-  </si>
-  <si>
-    <t>https://shopping-phinf.pstatic.net/main_5385862/53858622401.jpg</t>
-  </si>
-  <si>
-    <t>강아지 반려견 모발보습 털엉킴 방지 컨디셔너</t>
-  </si>
-  <si>
-    <t>https://smartstore.naver.com/main/products/11655387304</t>
-  </si>
-  <si>
-    <t>https://shopping-phinf.pstatic.net/main_8919989/89199897770.jpg</t>
-  </si>
-  <si>
-    <t>유라이샵</t>
-  </si>
-  <si>
-    <t>액체 비누 디펜서 리필 욕실 디스펜서 액세서리 플라 G2518ZA 접시 럭셔리 워시 오오마사토시 250ml</t>
-  </si>
-  <si>
-    <t>https://smartstore.naver.com/main/products/11655331392</t>
-  </si>
-  <si>
-    <t>https://shopping-phinf.pstatic.net/main_8919984/89199841858.jpg</t>
-  </si>
-  <si>
-    <t>롸맘직구</t>
-  </si>
-  <si>
     <t>강아지 배변용품</t>
   </si>
   <si>
     <t>배변봉투/집게</t>
   </si>
   <si>
-    <t>가능 핸드 욕실 가능한 개 디펜서 300/500ml 병 젤 샴푸 리필 비누 펌프 용기 재사용 샤워  300ml  green-4pcs  4개</t>
-  </si>
-  <si>
-    <t>https://link.coupang.com/re/PCSNAVERPCSDP?pageKey=8533463550&amp;ctag=8533463550&amp;lptag=I24397425245&amp;itemId=24397425245&amp;vendorItemId=91412310960&amp;spec=10305199</t>
-  </si>
-  <si>
-    <t>https://shopping-phinf.pstatic.net/main_5385852/53858521678.jpg</t>
-  </si>
-  <si>
-    <t>디스펜서</t>
-  </si>
-  <si>
-    <t>미국 크라운로얄 매직터치 그루밍스프레이 포뮬라3 원액1 대 물 15 비숑 포메 셀티 단모 파상모 테리어  1개  473ml</t>
-  </si>
-  <si>
-    <t>https://link.coupang.com/re/PCSNAVERPCSDP?pageKey=7690200212&amp;ctag=7690200212&amp;lptag=V82570567170&amp;itemId=20563081160&amp;vendorItemId=82570567170&amp;spec=10305199</t>
-  </si>
-  <si>
-    <t>https://shopping-phinf.pstatic.net/main_5385839/53858391642.jpg</t>
-  </si>
-  <si>
-    <t>반려동물 마루 코팅제 500ml</t>
-  </si>
-  <si>
-    <t>https://link.coupang.com/re/PCSNAVERPCSDP?pageKey=4320780180&amp;ctag=4320780180&amp;lptag=I25168939706&amp;itemId=25168939706&amp;vendorItemId=92186685780&amp;spec=10305199</t>
-  </si>
-  <si>
-    <t>https://shopping-phinf.pstatic.net/main_5385838/53858387095.jpg</t>
-  </si>
-  <si>
-    <t>린레이</t>
-  </si>
-  <si>
-    <t>자동 손세정기 샤워 비오레 비누 손세정제 비둘기핸드워시 센서 세정제 White 디스펜서  콜라보레이션-강아지 스탠다드핏 +벽걸이+손 세정제  1개</t>
-  </si>
-  <si>
-    <t>https://link.coupang.com/re/PCSNAVERPCSDP?pageKey=8579277330&amp;ctag=8579277330&amp;lptag=P8579277330&amp;itemId=24865506408&amp;vendorItemId=91872499335&amp;spec=10305199</t>
-  </si>
-  <si>
-    <t>https://shopping-phinf.pstatic.net/main_5385832/53858324859.jpg</t>
-  </si>
-  <si>
-    <t>강아지발도장 동물 고양이 강아지 발자국 아크릴 스탬프 비누 엠보싱 장 각인 수제 1PC</t>
-  </si>
-  <si>
-    <t>https://www.11st.co.kr/connect/Gateway.tmall?method=Xsite&amp;prdNo=8137345774&amp;tid=1000000061</t>
-  </si>
-  <si>
-    <t>https://shopping-phinf.pstatic.net/main_5385828/53858287681.jpg</t>
-  </si>
-  <si>
-    <t>11번가</t>
-  </si>
-  <si>
     <t>문구/사무용품</t>
-  </si>
-  <si>
-    <t>스탬프/도장</t>
-  </si>
-  <si>
-    <t>스탬프</t>
-  </si>
-  <si>
-    <t>2마리의 작은 개와 2마리의 고양이를 위한 럭셔리 그레이 직사각형 애완동물 침대, 비누가 닿지 않는 바닥이 있는 슈퍼 소프트 세탁 가능한 더블 고양이 침대, 실내 사용을 위한</t>
-  </si>
-  <si>
-    <t>https://temuaffiliateprogram.pxf.io/c/5257454/1580294/18350?u=https%3A%2F%2Fwww.temu.com%2Fkr%2Fgoods.html%3Fsku_id%3D17592913576699%26goods_id%3D601099700795413%26_x_ns_catalog_id%3D10000%26_x_ns_product_id%3D17592913576699%26_x_ns_site_id%3D119%26_x_ns_ad%3d{ad}</t>
-  </si>
-  <si>
-    <t>https://shopping-phinf.pstatic.net/main_5385827/53858277897.jpg</t>
-  </si>
-  <si>
-    <t>리빙용품</t>
-  </si>
-  <si>
-    <t>쿠션/방석</t>
-  </si>
-  <si>
-    <t>크리스탈 에폭시 수지 금형 수제 석고 비누 곰팡이 천사 날강아지 모양</t>
-  </si>
-  <si>
-    <t>https://www.11st.co.kr/connect/Gateway.tmall?method=Xsite&amp;prdNo=8137406874&amp;tid=1000000061</t>
-  </si>
-  <si>
-    <t>https://shopping-phinf.pstatic.net/main_5385827/53858271216.jpg</t>
-  </si>
-  <si>
-    <t>아로마/캔들용품</t>
-  </si>
-  <si>
-    <t>기타아로마/캔들용품</t>
-  </si>
-  <si>
-    <t>바란스 개세정액 화이트워시 브라이트 백모용 503ml</t>
-  </si>
-  <si>
-    <t>https://smartstore.naver.com/main/products/11655271806</t>
-  </si>
-  <si>
-    <t>https://shopping-phinf.pstatic.net/main_8919978/89199782272.jpg</t>
-  </si>
-  <si>
-    <t>We-Wit</t>
-  </si>
-  <si>
-    <t>크래프트 상자 블랙 화이트 포장 판지 축제 파티 비누 개 50 선물</t>
-  </si>
-  <si>
-    <t>https://smartstore.naver.com/main/products/11655271746</t>
-  </si>
-  <si>
-    <t>https://shopping-phinf.pstatic.net/main_8919978/89199782212.jpg</t>
-  </si>
-  <si>
-    <t>nninecp</t>
-  </si>
-  <si>
-    <t>소형기계</t>
-  </si>
-  <si>
-    <t>기타소형기계</t>
-  </si>
-  <si>
-    <t>2025-03-30 15:56:04 기준</t>
-  </si>
-  <si>
-    <t xml:space="preserve">prev_list와 now_list의 비교를 통해 다음과 같은 주요 특징을 도출할 수 있습니다.
-우선, 'image' 항목에 있는 이미지 URL이 prev_list와 now_list에서 차이가 있습니다. 예를 들어, 1위 상품 '개 대 정장 샴푸 프레스 대비누대 비누 블랙 치솔 칫솔 세트'의 이미지 URL이 prev_list에서는 'https://shopping-phinf.pstatic.net/main_5385874/53858743882.jpg'인 반면 now_list에서는 'https://shopping-phinf.pstatic.net/main_5385874/53858743882.jpg'으로 변경되지 않았습니다. 이는 이미지 품질이나 저장 경로의 안정성을 의미할 수 있습니다.
-가격 측면에서는 두 목록 모두 동일한 가격 정보를 제공하며, 특히 1위 상품은 23920원이 유지되고 있습니다. 쇼핑몰 정보는 또한 변동이 없으며, 1위부터 20위까지의 상품은 모두 '옥션', '쿠팡', 'TEMU kr', '11번가'와 같은 사이트에서 판매되고 있습니다.
-특히 다수의 상품이 '생활/건강' 카테고리 내에서 '반려동물' 관련 제품으로 분류되어 있으며, 20위까지의 상품 중 반려동물 관련 제품이 과반수 이상을 차지하고 있습니다. 이는 소비자들이 반려동물 제품에 대한 수요가 높아졌음을 반영합니다.
-결론적으로, prev_list와 now_list 간에는 큰 변화는 없지만 몇 가지 항목의 안정성과 반복된 반려동물 관련 제품의 출현이 눈에 띄며, 이는 현재 소비 트렌드와 관련이 깊다고 판단됩니다.
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">**올가홀푸드, 헬시 스낵 시장 진출**
-2025년 3월 21일, 올가홀푸드가 국내산 원물을 활용한 헬시 스낵 시장에 도전한다고 발표했다. 올가홀푸드는 건강을 중시하는 소비자 트렌드에 맞춰 고영양가 제품을 출시할 계획이다. 이를 통해 시장 점유율 확대를 목표로 하며, 특히 자연 재료와 무첨가 제품에 집중할 예정이다. 올가홀푸드는 독자적인 제조 공정을 통해 품질과 맛을 동시에 잡겠다는 전략을 세우고 있으며, 소비자들에게 직접 체험할 기회를 제공하는 이벤트도 계획 중이다. 이와 같은 혁신적인 접근은 헬시 스낵 분야의 경쟁을 더욱 치열하게 할 것으로 예상된다.
-</t>
   </si>
   <si>
     <t>OO Daily Insights</t>
@@ -747,6 +446,335 @@
   </si>
   <si>
     <t>hh</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>description</t>
+  </si>
+  <si>
+    <t>bloggername</t>
+  </si>
+  <si>
+    <t>bloggerlink</t>
+  </si>
+  <si>
+    <t>postdate</t>
+  </si>
+  <si>
+    <t>[상하이 여행] 하나 트래블로그 유니온페이 추천</t>
+  </si>
+  <si>
+    <t>https://blog.naver.com/binhaha0810/223951416688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">체크카드 &lt;b&gt;삼성카드&lt;/b&gt; 트래블 체크카드* NH농협 트래블 체크카드* 발급은행/사 하나은행 신한은행 KB국민은행 우리은행 &lt;b&gt;삼성카드&lt;/b&gt; 농협은행 환전 방식 트래블로그 앱 → 다중 통화 충전 SOL·트래블 앱... </t>
+  </si>
+  <si>
+    <t>백구의 모든것</t>
+  </si>
+  <si>
+    <t>blog.naver.com/binhaha0810</t>
+  </si>
+  <si>
+    <t>[계약금결제]테슬라 모델Y 롱레인지 계약서변경 발송</t>
+  </si>
+  <si>
+    <t>https://blog.naver.com/jjo_jae/223951417179</t>
+  </si>
+  <si>
+    <t xml:space="preserve">#테슬라 #모델Y #주니퍼 #롱레인지 #주행거리 #전기차 #배터리 #계약 #계약금 #500만원 #&lt;b&gt;삼성카드&lt;/b&gt; #발송 #메일 #변경사항 #동의 #8월입항 #차량배정 테슬라에서 갑작스레 문자를 보냈습니다. 마성의 테슬라..... </t>
+  </si>
+  <si>
+    <t>JJo_Jae 월드</t>
+  </si>
+  <si>
+    <t>blog.naver.com/jjo_jae</t>
+  </si>
+  <si>
+    <t>민생회복지원금 소비쿠폰 올리브영 가맹점 사용처 조회 꿀팁</t>
+  </si>
+  <si>
+    <t>https://blog.naver.com/okithekey/223951413804</t>
+  </si>
+  <si>
+    <t xml:space="preserve">카드사 앱 조회 신한카드, &lt;b&gt;삼성카드&lt;/b&gt;(모니모), BC카드(페이북) 등에서 ‘민생회복지원금 사용처 조회’ 메뉴 이용 지역과 상호명을 검색하면 리스트 확인 가능 ✅ 2. 올리브영 앱 &amp;amp; 홈페이지 앱 &amp;gt; [올영매장] 메뉴... </t>
+  </si>
+  <si>
+    <t>건강한 부자</t>
+  </si>
+  <si>
+    <t>blog.naver.com/okithekey</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[8월1일 OPEN] 다낭 메리어트 리조트앤스파 / 메리어트 논누억... </t>
+  </si>
+  <si>
+    <t>https://blog.naver.com/pure_8906/223951408970</t>
+  </si>
+  <si>
+    <t xml:space="preserve">- 카드 할인 중복 적용 가능 ※ 단, 하나투어 앱 전용 결제 시 가능 ※ 하나투어 회원 할인 가능 ※ 현재 확정 된 할인 적용 카드사 : &lt;b&gt;삼성카드&lt;/b&gt; 2. 메리어트 리조트앤스파 POINT. ✔️글로벌 5대 호텔 체인 중... </t>
+  </si>
+  <si>
+    <t>지운맘의 여행일기</t>
+  </si>
+  <si>
+    <t>blog.naver.com/pure_8906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">소비쿠폰 사용처 조회하는 방법, 민생회복지원금 무인매장도... </t>
+  </si>
+  <si>
+    <t>https://blog.naver.com/zero-eyes/223951407320</t>
+  </si>
+  <si>
+    <t xml:space="preserve">각 카드사와 지역페이 앱이나 홈페이지에서 지역과 매장명 미리 검색하면 소비쿠폰 사용 가능한지 확실히 알 수 있어요  ⬆️ 카드사 중 예시로 보여드리면 &lt;b&gt;삼성카드&lt;/b&gt; 홈페이지만 접속해도 위 사진처럼 바로... </t>
+  </si>
+  <si>
+    <t>제로아이즈 공식 블로그</t>
+  </si>
+  <si>
+    <t>blog.naver.com/zero-eyes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">이마트 트레이더스 고레잇템 할인행사 &amp;amp; 트레이더스 신상품... </t>
+  </si>
+  <si>
+    <t>https://blog.naver.com/skyblue-a/223951400709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">또는 &lt;b&gt;삼성카드&lt;/b&gt; 결제 시에 다양한 할인 혜택을 받을 수 있는 고레잇템 할인 행사가 진행됩니다.... 할인 &lt;b&gt;삼성카드&lt;/b&gt; 고객이라면 전자제품 할인 혜택도 누릴 수 있어요! • 다이슨 무선 청소기 MICRO : 71... </t>
+  </si>
+  <si>
+    <t>하루조아</t>
+  </si>
+  <si>
+    <t>blog.naver.com/skyblue-a</t>
+  </si>
+  <si>
+    <t>국민행복&lt;b&gt;카드&lt;/b&gt; 신청 후기 캐시백 이벤트 참여</t>
+  </si>
+  <si>
+    <t>https://blog.naver.com/jeong001116/223951397256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IBK, 삼성, 신한, KB 카드가 있었고 6개월 이내 발급받은 적이 없는 카드사인 &lt;b&gt;삼성카드&lt;/b&gt;로 신청했다 캐시백 사은품 지급 조건이 만족해야 받을 수 있기 때문에 행사 세부내용과 참여방법을 꼭 확인하고 신청해야... </t>
+  </si>
+  <si>
+    <t>모아가 블로그</t>
+  </si>
+  <si>
+    <t>blog.naver.com/jeong001116</t>
+  </si>
+  <si>
+    <t>&lt;b&gt;삼성카드&lt;/b&gt; 고객센터 전화번호 상담원 연결 통화안내</t>
+  </si>
+  <si>
+    <t>https://blog.naver.com/serdfbset/223951393805</t>
+  </si>
+  <si>
+    <t>&lt;b&gt;삼성카드&lt;/b&gt; 고객센터 전화번호  &lt;b&gt;삼성카드&lt;/b&gt; 고객센터 전화번호 상담원 연결 통화안내 국민카드 상담원연결 하는법 ▶ &lt;b&gt;삼성카드&lt;/b&gt; 상담원연결 하는법 ▶ 현대카드 상담원연결 하는법 ▶</t>
+  </si>
+  <si>
+    <t>호구와트</t>
+  </si>
+  <si>
+    <t>blog.naver.com/serdfbset</t>
+  </si>
+  <si>
+    <t>민생회복 &lt;b&gt;삼성카드&lt;/b&gt; 소비쿠폰 간편 신청 방법</t>
+  </si>
+  <si>
+    <t>https://blog.naver.com/mopadoll/223951393584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&lt;b&gt;삼성카드&lt;/b&gt;의 경우 앱에서 사용 내역과 남은 잔액을 확인할 수도 있다. 삼성페이, 네이버페이, 카카오페이 등에 카드를 연동해 놓으면 마찬가지로 자동으로 결제된다. 선불카드/상품권 방식 선불카드나... </t>
+  </si>
+  <si>
+    <t>MoRangMoRang</t>
+  </si>
+  <si>
+    <t>blog.naver.com/mopadoll</t>
+  </si>
+  <si>
+    <t>2025년 재산세 부과 기준,납부 방법 및 &lt;b&gt;카드&lt;/b&gt;납부 혜택</t>
+  </si>
+  <si>
+    <t>https://blog.naver.com/mlchy99/223951391783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1% 캐시백 국민카드 6 , 10개월 부분 무이자 전월실적 30만원 , 10만원이상 납부 시 7,000원 할인 &lt;b&gt;삼성카드&lt;/b&gt; 6, 10, 12개월 다이어트 할부 (개월수 별로 1-5회차 수수료 고객부담, 4~12회차 수수료 면제) 문자 고객... </t>
+  </si>
+  <si>
+    <t>은코이ʕ·ᴥ·ʔ</t>
+  </si>
+  <si>
+    <t>blog.naver.com/mlchy99</t>
+  </si>
+  <si>
+    <t>명당, 준비물, 어트랙션꿀팁!초등학생 조카들과 다녀온 후기</t>
+  </si>
+  <si>
+    <t>https://blog.naver.com/sido_log_/223951388934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">캐리비안베이 가기 전 준비사항 1⃣ 입장권 예약 ⦁ &lt;b&gt;삼성카드&lt;/b&gt;로 할인 가능! ⦁ 성수기엔 현장보다 사전... 조카들이 좋아하는 페트병 음료 ⦁ 껍질과 씨를 제거한 수박  캐리비안베이 당일 일정 &amp;amp; 동선 리뷰 오전... </t>
+  </si>
+  <si>
+    <t>시도로그</t>
+  </si>
+  <si>
+    <t>blog.naver.com/sido_log_</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[6주6일-8주6일] 처음 심장소리를 들었어요, 그리고... </t>
+  </si>
+  <si>
+    <t>https://blog.naver.com/mimi_newdays/223949950746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">나라에서 임산부 바우처 100만원을 충전해주는 카드를 만드는 것인데, 내가 만들 수 있는 카드사중에 혜택이 가장 좋아보이는 &lt;b&gt;삼성카드&lt;/b&gt;로 결정. 카드는 한 이틀만에 왔다. 그 다음으론 지역 보건소에 가서... </t>
+  </si>
+  <si>
+    <t>미미블로그</t>
+  </si>
+  <si>
+    <t>blog.naver.com/mimi_newdays</t>
+  </si>
+  <si>
+    <t>시몬스 구미점 초등학생 침대 매트리스 추천</t>
+  </si>
+  <si>
+    <t>https://blog.naver.com/yosulpp/223951384837</t>
+  </si>
+  <si>
+    <t xml:space="preserve">시몬스 페이로는 롯데/&lt;b&gt;삼성카드&lt;/b&gt; 36개월 무이자, 현대/신한/ 국민/하나카드 24개월 무이자. BC/우리/농협 12개월 무이자 및 심지어 네이버, 삼성, 애플 ,카카오 페이도 결제가 가능 하니 참고하셔유~~^^ 후기 요약... </t>
+  </si>
+  <si>
+    <t>태연자약</t>
+  </si>
+  <si>
+    <t>blog.naver.com/yosulpp</t>
+  </si>
+  <si>
+    <t>야놀자 할인 코드 7월 실시간 정리</t>
+  </si>
+  <si>
+    <t>https://blog.naver.com/hellotoday31/223951381780</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7월 결제 혜택 항공권 혜택 국제선 항공권에 대해 &lt;b&gt;삼성카드&lt;/b&gt;, 롯데카드, 하나카드, 신한카드, NH농협카드, KB국민카드로 결제 시 최대 15% 즉시 할인 혜택이 있습니다! 항공권 예약 링크 (Click!) Link... </t>
+  </si>
+  <si>
+    <t>헬로투데이</t>
+  </si>
+  <si>
+    <t>blog.naver.com/hellotoday31</t>
+  </si>
+  <si>
+    <t>백화점상품권 신용&lt;b&gt;카드&lt;/b&gt;결제 할부 정확하게 조회하기</t>
+  </si>
+  <si>
+    <t>https://blog.naver.com/kmwe6xico02s/223951380855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">이는 단순히 금액적 제한이 아니라 카드사의 정책에 따른 것으로, 현대카드, 신한카드, &lt;b&gt;삼성카드&lt;/b&gt; 등 대부분의 주요 카드사가 동일한 기준을 적용하고 있을꺼에요. 중요한 점은 이 한도가 카드사별로 독립적으로... </t>
+  </si>
+  <si>
+    <t>아름다운 세계여행</t>
+  </si>
+  <si>
+    <t>blog.naver.com/kmwe6xico02s</t>
+  </si>
+  <si>
+    <t>대구신혼침대비교 겟팅후기✨ 동생과 함께 다녀옴~</t>
+  </si>
+  <si>
+    <t>https://blog.naver.com/32sjdqls/223951379073</t>
+  </si>
+  <si>
+    <t xml:space="preserve">무이자 최대 24개월 할부 (&lt;b&gt;삼성카드&lt;/b&gt; 기준) (예로 : 아우로라 매트리스는 월 49,590원으로 부담 낮춰서 구매 가능!)  구매금액대별 사은품 증정! 최대 90만원 상당의 1인용 안락소파까지   이벤트 매트리스 구매 시... </t>
+  </si>
+  <si>
+    <t>2월29일 하루더하기</t>
+  </si>
+  <si>
+    <t>blog.naver.com/32sjdqls</t>
+  </si>
+  <si>
+    <t>마이리얼트립 2025년 7월 이벤트와 쿠폰들을 모아서 정리했어요</t>
+  </si>
+  <si>
+    <t>https://blog.naver.com/blendtour/223951377151</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7월 신용 카드 결제 수단 추가 혜택 (숙소, 투어, 티켓) - 업데이트 완료 네이버페이, 토스 페이먼츠, 토스 페이(toss pay), 카카오페이, &lt;b&gt;삼성카드&lt;/b&gt;, BC카드, 현대카드, 우리 WON 페이, 우리카드, 하나카드... </t>
+  </si>
+  <si>
+    <t>Blendtour</t>
+  </si>
+  <si>
+    <t>blog.naver.com/blendtour</t>
+  </si>
+  <si>
+    <t>유레일패스 종류 유로스타 TGV 예약 방법 1등석 가격 할인코드</t>
+  </si>
+  <si>
+    <t>https://blog.naver.com/bian258/223951374912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">현대카드, 네이버페이, 비씨카드, &lt;b&gt;삼성카드&lt;/b&gt;, 롯데카드 등이 있는데요. 카드사별로 최소 2천원부터 최대 4만원까지 할인받을 수 있습니다. 클룩의 경우 유레일패스 구매한 모든 사람들에게 유럽esim(3GB, 30일)... </t>
+  </si>
+  <si>
+    <t>지구는 둥그니까</t>
+  </si>
+  <si>
+    <t>blog.naver.com/bian258</t>
+  </si>
+  <si>
+    <t>&lt;b&gt;삼성&lt;/b&gt; 노마드&lt;b&gt;카드&lt;/b&gt; 최대 2% 빅포인트 적립 방법</t>
+  </si>
+  <si>
+    <t>https://blog.naver.com/most2013/223951373405</t>
+  </si>
+  <si>
+    <t xml:space="preserve">특히 여행과 쇼핑을 즐기시는 분들께는 삼성 노마드카드가 유용한 선택이 될 수 있습니다. 국내 전용은... 이 카드에 대해 더 알아보고 싶으시거나 다른 &lt;b&gt;삼성카드&lt;/b&gt; 라인업도 함께 검토하고 싶으시다면 &lt;b&gt;삼성카드&lt;/b&gt;... </t>
+  </si>
+  <si>
+    <t>기분좋은날</t>
+  </si>
+  <si>
+    <t>blog.naver.com/most2013</t>
+  </si>
+  <si>
+    <t>부담경감 크레딧! 소상공인 50만원 지원</t>
+  </si>
+  <si>
+    <t>https://blog.naver.com/nomusa911/223950987675</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31(수)까지 사용처 공과금 전기/가스/수도 4대보험료 사업주 부담액 신청 카드사 국민카드, 농협카드, 롯데카드, 비씨카드, &lt;b&gt;삼성카드&lt;/b&gt;, 신한카드, 우리카드, 전북은행 국민카드, 하나카드, 현대카드 관련해... </t>
+  </si>
+  <si>
+    <t>사업주 전문노무사 (사장님의 권리를 지켜드립니다.)</t>
+  </si>
+  <si>
+    <t>blog.naver.com/nomusa911</t>
+  </si>
+  <si>
+    <t>2025-07-29 17:53:36 기준</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>prev_list는 반려동물 관련 상품 중심(배변용품, 사료, 간식 등)으로 ‘모두의 서락’, ‘도마뱀용품점’ 같은 전문몰과 ‘생활/건강’ 카테고리에 집중되어 있으며, 가격 범위는 890원부터 237,800원까지 다양했다. 반면 now_list는 ‘삼성카드’ 관련 블로그 글 중심으로, 카드 혜택, 여행, 할인정보, 캐시백 등 금융 및 라이프스타일 주제로 전환되었고, 쇼핑몰 정보 대신 블로거명과 포스트 날짜(2025년 7월 29일 기준)가 포함되었다. 즉, 상품 판매 중심에서 콘텐츠 정보 제공 및 카드사 홍보 중심으로 주요 특징이 변화했다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>- 2025년 상반기 국내 6개 카드사(신한·삼성·KB국민·현대·하나·우리)의 당기순이익 합계는 1조1152억 원으로, 전년 동기 1조3622억 원 대비 18.1%(2470억 원) 감소했다.  
+- 신한카드는 35%, KB국민카드 29.1%, 우리카드 9.5%, 삼성카드 7.5%, 하나카드 5.5% 순이익이 줄었으며, 현대카드는 1% 소폭 성장했다.  
+- 2분기 합산 순이익은 5589억 원으로 전년 동기 대비 22% 감소했다.  
+- 삼성카드는 3356억 원의 순이익을 기록하며 1위를 유지했으나 전년 동기 대비 7.5% 감소했다.  
+- 카드사들은 대손충당금 확대와 비용 부담 증가 등으로 수익성 악화에 직면했으며, 하반기에는 소비자 혜택 축소 가능성이 제기된다.  
+- 한편, 대구시는 8월 1일부터 지역화폐 ‘대구로페이’를 2800억 원 규모로 발행, 월 50만 원 한도 내에서 기본 7% 할인에 ‘대구로’ 앱 결제 시 추가 5% 할인을 제공해 최대 12% 할인 혜택을 제공한다.</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1234,55 +1262,6 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <sheetPr>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A1:A8"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="1" max="1" width="85.625" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:1" ht="38.25" x14ac:dyDescent="0.3">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A3" s="6" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="4" spans="1:1" ht="20.25" x14ac:dyDescent="0.3">
-      <c r="A4" s="2" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:1" ht="345" x14ac:dyDescent="0.3">
-      <c r="A5" s="5" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="6" spans="1:1" ht="37.5" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="7" spans="1:1" ht="20.25" x14ac:dyDescent="0.3">
-      <c r="A7" s="2" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="8" spans="1:1" s="3" customFormat="1" ht="155.25" x14ac:dyDescent="0.3">
-      <c r="A8" s="5" t="s">
-        <v>122</v>
-      </c>
-    </row>
-  </sheetData>
-  <phoneticPr fontId="1" type="noConversion"/>
-  <pageMargins left="0.5" right="0.42" top="0.75" bottom="0.28999999999999998" header="0.3" footer="0.44"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
@@ -1300,7 +1279,7 @@
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A3" s="6" t="s">
-        <v>124</v>
+        <v>236</v>
       </c>
     </row>
     <row r="4" spans="1:1" ht="20.25" x14ac:dyDescent="0.3">
@@ -1308,9 +1287,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:1" ht="362.25" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:1" ht="103.5" x14ac:dyDescent="0.3">
       <c r="A5" s="5" t="s">
-        <v>127</v>
+        <v>237</v>
       </c>
     </row>
     <row r="6" spans="1:1" ht="37.5" customHeight="1" x14ac:dyDescent="0.3"/>
@@ -1319,9 +1298,58 @@
         <v>2</v>
       </c>
     </row>
+    <row r="8" spans="1:1" s="3" customFormat="1" ht="207" x14ac:dyDescent="0.3">
+      <c r="A8" s="5" t="s">
+        <v>238</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.5" right="0.42" top="0.75" bottom="0.28999999999999998" header="0.3" footer="0.44"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{546E3945-C4F0-4A09-9FA1-C25D0F996777}">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:A8"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="85.625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:1" ht="38.25" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A3" s="6" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1" ht="20.25" x14ac:dyDescent="0.3">
+      <c r="A4" s="2" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1" ht="362.25" x14ac:dyDescent="0.3">
+      <c r="A5" s="5" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1" ht="37.5" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="7" spans="1:1" ht="20.25" x14ac:dyDescent="0.3">
+      <c r="A7" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
     <row r="8" spans="1:1" s="3" customFormat="1" ht="155.25" x14ac:dyDescent="0.3">
       <c r="A8" s="5" t="s">
-        <v>130</v>
+        <v>32</v>
       </c>
     </row>
   </sheetData>
@@ -1344,33 +1372,33 @@
   <sheetData>
     <row r="1" spans="1:1" ht="38.25" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>123</v>
+        <v>25</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A3" s="7" t="s">
-        <v>125</v>
+        <v>27</v>
       </c>
     </row>
     <row r="4" spans="1:1" ht="20.25" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
-        <v>126</v>
+        <v>28</v>
       </c>
     </row>
     <row r="5" spans="1:1" ht="362.25" x14ac:dyDescent="0.3">
       <c r="A5" s="5" t="s">
-        <v>128</v>
+        <v>30</v>
       </c>
     </row>
     <row r="6" spans="1:1" ht="37.5" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="7" spans="1:1" ht="20.25" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="s">
-        <v>129</v>
+        <v>31</v>
       </c>
     </row>
     <row r="8" spans="1:1" s="3" customFormat="1" ht="207" x14ac:dyDescent="0.3">
       <c r="A8" s="5" t="s">
-        <v>131</v>
+        <v>33</v>
       </c>
     </row>
   </sheetData>
@@ -1382,10 +1410,10 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
-  <dimension ref="A1:O21"/>
+  <dimension ref="A1:G21"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>3</v>
       </c>
@@ -1396,794 +1424,476 @@
         <v>5</v>
       </c>
       <c r="D1" t="s">
+        <v>132</v>
+      </c>
+      <c r="E1" t="s">
+        <v>133</v>
+      </c>
+      <c r="F1" t="s">
+        <v>134</v>
+      </c>
+      <c r="G1" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2" t="s">
+        <v>136</v>
+      </c>
+      <c r="C2" t="s">
+        <v>137</v>
+      </c>
+      <c r="D2" t="s">
+        <v>138</v>
+      </c>
+      <c r="E2" t="s">
+        <v>139</v>
+      </c>
+      <c r="F2" t="s">
+        <v>140</v>
+      </c>
+      <c r="G2">
+        <v>20250729</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A3">
+        <v>2</v>
+      </c>
+      <c r="B3" t="s">
+        <v>141</v>
+      </c>
+      <c r="C3" t="s">
+        <v>142</v>
+      </c>
+      <c r="D3" t="s">
+        <v>143</v>
+      </c>
+      <c r="E3" t="s">
+        <v>144</v>
+      </c>
+      <c r="F3" t="s">
+        <v>145</v>
+      </c>
+      <c r="G3">
+        <v>20250729</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A4">
+        <v>3</v>
+      </c>
+      <c r="B4" t="s">
+        <v>146</v>
+      </c>
+      <c r="C4" t="s">
+        <v>147</v>
+      </c>
+      <c r="D4" t="s">
+        <v>148</v>
+      </c>
+      <c r="E4" t="s">
+        <v>149</v>
+      </c>
+      <c r="F4" t="s">
+        <v>150</v>
+      </c>
+      <c r="G4">
+        <v>20250729</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A5">
+        <v>4</v>
+      </c>
+      <c r="B5" t="s">
+        <v>151</v>
+      </c>
+      <c r="C5" t="s">
+        <v>152</v>
+      </c>
+      <c r="D5" t="s">
+        <v>153</v>
+      </c>
+      <c r="E5" t="s">
+        <v>154</v>
+      </c>
+      <c r="F5" t="s">
+        <v>155</v>
+      </c>
+      <c r="G5">
+        <v>20250729</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A6">
+        <v>5</v>
+      </c>
+      <c r="B6" t="s">
+        <v>156</v>
+      </c>
+      <c r="C6" t="s">
+        <v>157</v>
+      </c>
+      <c r="D6" t="s">
+        <v>158</v>
+      </c>
+      <c r="E6" t="s">
+        <v>159</v>
+      </c>
+      <c r="F6" t="s">
+        <v>160</v>
+      </c>
+      <c r="G6">
+        <v>20250729</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A7">
         <v>6</v>
       </c>
-      <c r="E1" t="s">
+      <c r="B7" t="s">
+        <v>161</v>
+      </c>
+      <c r="C7" t="s">
+        <v>162</v>
+      </c>
+      <c r="D7" t="s">
+        <v>163</v>
+      </c>
+      <c r="E7" t="s">
+        <v>164</v>
+      </c>
+      <c r="F7" t="s">
+        <v>165</v>
+      </c>
+      <c r="G7">
+        <v>20250729</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A8">
         <v>7</v>
       </c>
-      <c r="F1" t="s">
+      <c r="B8" t="s">
+        <v>166</v>
+      </c>
+      <c r="C8" t="s">
+        <v>167</v>
+      </c>
+      <c r="D8" t="s">
+        <v>168</v>
+      </c>
+      <c r="E8" t="s">
+        <v>169</v>
+      </c>
+      <c r="F8" t="s">
+        <v>170</v>
+      </c>
+      <c r="G8">
+        <v>20250729</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A9">
         <v>8</v>
       </c>
-      <c r="G1" t="s">
-        <v>9</v>
-      </c>
-      <c r="H1" t="s">
-        <v>10</v>
-      </c>
-      <c r="I1" t="s">
-        <v>11</v>
-      </c>
-      <c r="J1" t="s">
-        <v>12</v>
-      </c>
-      <c r="K1" t="s">
-        <v>13</v>
-      </c>
-      <c r="L1" t="s">
-        <v>14</v>
-      </c>
-      <c r="M1" t="s">
-        <v>15</v>
-      </c>
-      <c r="N1" t="s">
-        <v>16</v>
-      </c>
-      <c r="O1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="2" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
-        <v>228</v>
-      </c>
-      <c r="B2" t="s">
-        <v>132</v>
-      </c>
-      <c r="C2" t="s">
-        <v>133</v>
-      </c>
-      <c r="D2" t="s">
-        <v>134</v>
-      </c>
-      <c r="E2">
-        <v>57480</v>
-      </c>
-      <c r="G2" t="s">
-        <v>135</v>
-      </c>
-      <c r="H2">
-        <v>89588404320</v>
-      </c>
-      <c r="I2">
-        <v>2</v>
-      </c>
-      <c r="L2" t="s">
-        <v>20</v>
-      </c>
-      <c r="M2" t="s">
-        <v>21</v>
-      </c>
-      <c r="N2" t="s">
-        <v>77</v>
-      </c>
-      <c r="O2" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="3" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
-        <v>228</v>
-      </c>
-      <c r="B3" t="s">
-        <v>137</v>
-      </c>
-      <c r="C3" t="s">
-        <v>138</v>
-      </c>
-      <c r="D3" t="s">
-        <v>139</v>
-      </c>
-      <c r="E3">
-        <v>15000</v>
-      </c>
-      <c r="G3" t="s">
-        <v>140</v>
-      </c>
-      <c r="H3">
-        <v>89588437193</v>
-      </c>
-      <c r="I3">
-        <v>2</v>
-      </c>
-      <c r="L3" t="s">
-        <v>20</v>
-      </c>
-      <c r="M3" t="s">
-        <v>21</v>
-      </c>
-      <c r="N3" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="4" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
-        <v>228</v>
-      </c>
-      <c r="B4" t="s">
-        <v>141</v>
-      </c>
-      <c r="C4" t="s">
-        <v>142</v>
-      </c>
-      <c r="D4" t="s">
-        <v>143</v>
-      </c>
-      <c r="E4">
-        <v>2130</v>
-      </c>
-      <c r="G4" t="s">
-        <v>144</v>
-      </c>
-      <c r="H4">
-        <v>89588314106</v>
-      </c>
-      <c r="I4">
-        <v>2</v>
-      </c>
-      <c r="K4" t="s">
-        <v>145</v>
-      </c>
-      <c r="L4" t="s">
-        <v>20</v>
-      </c>
-      <c r="M4" t="s">
-        <v>21</v>
-      </c>
-      <c r="N4" t="s">
-        <v>77</v>
-      </c>
-      <c r="O4" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
-        <v>228</v>
-      </c>
-      <c r="B5" t="s">
-        <v>146</v>
-      </c>
-      <c r="C5" t="s">
-        <v>147</v>
-      </c>
-      <c r="D5" t="s">
-        <v>148</v>
-      </c>
-      <c r="E5">
-        <v>1880</v>
-      </c>
-      <c r="G5" t="s">
-        <v>135</v>
-      </c>
-      <c r="H5">
-        <v>89588436097</v>
-      </c>
-      <c r="I5">
-        <v>2</v>
-      </c>
-      <c r="L5" t="s">
-        <v>20</v>
-      </c>
-      <c r="M5" t="s">
-        <v>21</v>
-      </c>
-      <c r="N5" t="s">
-        <v>149</v>
-      </c>
-      <c r="O5" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A6" t="s">
-        <v>228</v>
-      </c>
-      <c r="B6" t="s">
-        <v>151</v>
-      </c>
-      <c r="C6" t="s">
-        <v>152</v>
-      </c>
-      <c r="D6" t="s">
-        <v>153</v>
-      </c>
-      <c r="E6">
-        <v>5780</v>
-      </c>
-      <c r="G6" t="s">
-        <v>154</v>
-      </c>
-      <c r="H6">
-        <v>89588435755</v>
-      </c>
-      <c r="I6">
-        <v>2</v>
-      </c>
-      <c r="L6" t="s">
-        <v>20</v>
-      </c>
-      <c r="M6" t="s">
-        <v>21</v>
-      </c>
-      <c r="N6" t="s">
-        <v>155</v>
-      </c>
-      <c r="O6" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A7" t="s">
-        <v>229</v>
-      </c>
-      <c r="B7" t="s">
-        <v>157</v>
-      </c>
-      <c r="C7" t="s">
-        <v>158</v>
-      </c>
-      <c r="D7" t="s">
-        <v>159</v>
-      </c>
-      <c r="E7">
-        <v>2000</v>
-      </c>
-      <c r="G7" t="s">
-        <v>160</v>
-      </c>
-      <c r="H7">
-        <v>89588305151</v>
-      </c>
-      <c r="I7">
-        <v>2</v>
-      </c>
-      <c r="K7" t="s">
-        <v>161</v>
-      </c>
-      <c r="L7" t="s">
-        <v>20</v>
-      </c>
-      <c r="M7" t="s">
-        <v>21</v>
-      </c>
-      <c r="N7" t="s">
-        <v>77</v>
-      </c>
-      <c r="O7" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A8" t="s">
-        <v>228</v>
-      </c>
-      <c r="B8" t="s">
-        <v>163</v>
-      </c>
-      <c r="C8" t="s">
-        <v>164</v>
-      </c>
-      <c r="D8" t="s">
-        <v>165</v>
-      </c>
-      <c r="E8">
-        <v>8380</v>
-      </c>
-      <c r="G8" t="s">
-        <v>166</v>
-      </c>
-      <c r="H8">
-        <v>89588433170</v>
-      </c>
-      <c r="I8">
-        <v>2</v>
-      </c>
-      <c r="K8" t="s">
-        <v>167</v>
-      </c>
-      <c r="L8" t="s">
-        <v>20</v>
-      </c>
-      <c r="M8" t="s">
-        <v>21</v>
-      </c>
-      <c r="N8" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A9" t="s">
-        <v>228</v>
-      </c>
       <c r="B9" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="C9" t="s">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="D9" t="s">
-        <v>170</v>
-      </c>
-      <c r="E9">
-        <v>51900</v>
-      </c>
-      <c r="G9" t="s">
-        <v>135</v>
-      </c>
-      <c r="H9">
-        <v>89588433426</v>
-      </c>
-      <c r="I9">
-        <v>2</v>
-      </c>
-      <c r="L9" t="s">
-        <v>20</v>
-      </c>
-      <c r="M9" t="s">
-        <v>21</v>
-      </c>
-      <c r="N9" t="s">
-        <v>171</v>
-      </c>
-      <c r="O9" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.3">
+        <v>173</v>
+      </c>
+      <c r="E9" t="s">
+        <v>174</v>
+      </c>
+      <c r="F9" t="s">
+        <v>175</v>
+      </c>
+      <c r="G9">
+        <v>20250729</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="C10" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="D10" t="s">
-        <v>175</v>
-      </c>
-      <c r="E10">
-        <v>9900</v>
-      </c>
-      <c r="G10" t="s">
-        <v>176</v>
-      </c>
-      <c r="H10">
-        <v>89588302111</v>
-      </c>
-      <c r="I10">
-        <v>2</v>
-      </c>
-      <c r="L10" t="s">
-        <v>20</v>
-      </c>
-      <c r="M10" t="s">
-        <v>97</v>
-      </c>
-      <c r="N10" t="s">
-        <v>177</v>
-      </c>
-      <c r="O10" t="s">
         <v>178</v>
       </c>
-    </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="E10" t="s">
+        <v>179</v>
+      </c>
+      <c r="F10" t="s">
+        <v>180</v>
+      </c>
+      <c r="G10">
+        <v>20250729</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="C11" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="D11" t="s">
-        <v>181</v>
-      </c>
-      <c r="E11">
-        <v>76330</v>
-      </c>
-      <c r="G11" t="s">
-        <v>182</v>
-      </c>
-      <c r="H11">
-        <v>89588432654</v>
-      </c>
-      <c r="I11">
-        <v>2</v>
-      </c>
-      <c r="L11" t="s">
-        <v>20</v>
-      </c>
-      <c r="M11" t="s">
-        <v>21</v>
-      </c>
-      <c r="N11" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.3">
+        <v>183</v>
+      </c>
+      <c r="E11" t="s">
+        <v>184</v>
+      </c>
+      <c r="F11" t="s">
+        <v>185</v>
+      </c>
+      <c r="G11">
+        <v>20250729</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A12">
         <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="C12" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="D12" t="s">
-        <v>185</v>
-      </c>
-      <c r="E12">
-        <v>16000</v>
-      </c>
-      <c r="G12" t="s">
-        <v>140</v>
-      </c>
-      <c r="H12">
-        <v>89588431561</v>
-      </c>
-      <c r="I12">
-        <v>2</v>
-      </c>
-      <c r="L12" t="s">
-        <v>20</v>
-      </c>
-      <c r="M12" t="s">
-        <v>21</v>
-      </c>
-      <c r="N12" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="13" spans="1:15" x14ac:dyDescent="0.3">
+        <v>188</v>
+      </c>
+      <c r="E12" t="s">
+        <v>189</v>
+      </c>
+      <c r="F12" t="s">
+        <v>190</v>
+      </c>
+      <c r="G12">
+        <v>20250729</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A13">
         <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>186</v>
+        <v>191</v>
       </c>
       <c r="C13" t="s">
-        <v>187</v>
+        <v>192</v>
       </c>
       <c r="D13" t="s">
-        <v>188</v>
-      </c>
-      <c r="E13">
-        <v>16650</v>
-      </c>
-      <c r="G13" t="s">
-        <v>189</v>
-      </c>
-      <c r="H13">
-        <v>89588431280</v>
-      </c>
-      <c r="I13">
-        <v>2</v>
-      </c>
-      <c r="K13" t="s">
-        <v>190</v>
-      </c>
-      <c r="L13" t="s">
-        <v>20</v>
-      </c>
-      <c r="M13" t="s">
-        <v>21</v>
-      </c>
-      <c r="N13" t="s">
-        <v>77</v>
-      </c>
-      <c r="O13" t="s">
-        <v>191</v>
-      </c>
-    </row>
-    <row r="14" spans="1:15" x14ac:dyDescent="0.3">
+        <v>193</v>
+      </c>
+      <c r="E13" t="s">
+        <v>194</v>
+      </c>
+      <c r="F13" t="s">
+        <v>195</v>
+      </c>
+      <c r="G13">
+        <v>20250729</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A14">
         <v>13</v>
       </c>
       <c r="B14" t="s">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="C14" t="s">
-        <v>193</v>
+        <v>197</v>
       </c>
       <c r="D14" t="s">
-        <v>194</v>
-      </c>
-      <c r="E14">
-        <v>5500</v>
-      </c>
-      <c r="G14" t="s">
-        <v>195</v>
-      </c>
-      <c r="H14">
-        <v>89588388722</v>
-      </c>
-      <c r="I14">
-        <v>2</v>
-      </c>
-      <c r="L14" t="s">
-        <v>20</v>
-      </c>
-      <c r="M14" t="s">
-        <v>21</v>
-      </c>
-      <c r="N14" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="15" spans="1:15" x14ac:dyDescent="0.3">
+        <v>198</v>
+      </c>
+      <c r="E14" t="s">
+        <v>199</v>
+      </c>
+      <c r="F14" t="s">
+        <v>200</v>
+      </c>
+      <c r="G14">
+        <v>20250729</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A15">
         <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>196</v>
+        <v>201</v>
       </c>
       <c r="C15" t="s">
-        <v>197</v>
+        <v>202</v>
       </c>
       <c r="D15" t="s">
-        <v>198</v>
-      </c>
-      <c r="E15">
-        <v>60120</v>
-      </c>
-      <c r="G15" t="s">
-        <v>199</v>
-      </c>
-      <c r="H15">
-        <v>89588430610</v>
-      </c>
-      <c r="I15">
-        <v>2</v>
-      </c>
-      <c r="L15" t="s">
-        <v>20</v>
-      </c>
-      <c r="M15" t="s">
-        <v>21</v>
-      </c>
-      <c r="N15" t="s">
-        <v>149</v>
-      </c>
-      <c r="O15" t="s">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="16" spans="1:15" x14ac:dyDescent="0.3">
+        <v>203</v>
+      </c>
+      <c r="E15" t="s">
+        <v>204</v>
+      </c>
+      <c r="F15" t="s">
+        <v>205</v>
+      </c>
+      <c r="G15">
+        <v>20250729</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A16">
         <v>15</v>
       </c>
       <c r="B16" t="s">
-        <v>201</v>
+        <v>206</v>
       </c>
       <c r="C16" t="s">
-        <v>202</v>
+        <v>207</v>
       </c>
       <c r="D16" t="s">
-        <v>203</v>
-      </c>
-      <c r="E16">
-        <v>11700</v>
-      </c>
-      <c r="G16" t="s">
-        <v>204</v>
-      </c>
-      <c r="H16">
-        <v>89588429695</v>
-      </c>
-      <c r="I16">
-        <v>2</v>
-      </c>
-      <c r="L16" t="s">
-        <v>20</v>
-      </c>
-      <c r="M16" t="s">
-        <v>21</v>
-      </c>
-      <c r="N16" t="s">
-        <v>205</v>
-      </c>
-      <c r="O16" t="s">
-        <v>206</v>
-      </c>
-    </row>
-    <row r="17" spans="1:15" x14ac:dyDescent="0.3">
+        <v>208</v>
+      </c>
+      <c r="E16" t="s">
+        <v>209</v>
+      </c>
+      <c r="F16" t="s">
+        <v>210</v>
+      </c>
+      <c r="G16">
+        <v>20250729</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A17">
         <v>16</v>
       </c>
       <c r="B17" t="s">
-        <v>207</v>
+        <v>211</v>
       </c>
       <c r="C17" t="s">
-        <v>208</v>
+        <v>212</v>
       </c>
       <c r="D17" t="s">
-        <v>209</v>
-      </c>
-      <c r="E17">
-        <v>237800</v>
-      </c>
-      <c r="G17" t="s">
-        <v>210</v>
-      </c>
-      <c r="H17">
-        <v>89588429526</v>
-      </c>
-      <c r="I17">
-        <v>2</v>
-      </c>
-      <c r="L17" t="s">
-        <v>20</v>
-      </c>
-      <c r="M17" t="s">
-        <v>211</v>
-      </c>
-      <c r="N17" t="s">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="18" spans="1:15" x14ac:dyDescent="0.3">
+        <v>213</v>
+      </c>
+      <c r="E17" t="s">
+        <v>214</v>
+      </c>
+      <c r="F17" t="s">
+        <v>215</v>
+      </c>
+      <c r="G17">
+        <v>20250729</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A18">
         <v>17</v>
       </c>
       <c r="B18" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="C18" t="s">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="D18" t="s">
-        <v>215</v>
-      </c>
-      <c r="E18">
-        <v>1080</v>
-      </c>
-      <c r="G18" t="s">
-        <v>166</v>
-      </c>
-      <c r="H18">
-        <v>89588429160</v>
-      </c>
-      <c r="I18">
-        <v>2</v>
-      </c>
-      <c r="L18" t="s">
-        <v>20</v>
-      </c>
-      <c r="M18" t="s">
-        <v>21</v>
-      </c>
-      <c r="N18" t="s">
-        <v>77</v>
-      </c>
-      <c r="O18" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="19" spans="1:15" x14ac:dyDescent="0.3">
+        <v>218</v>
+      </c>
+      <c r="E18" t="s">
+        <v>219</v>
+      </c>
+      <c r="F18" t="s">
+        <v>220</v>
+      </c>
+      <c r="G18">
+        <v>20250729</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A19">
         <v>18</v>
       </c>
       <c r="B19" t="s">
-        <v>216</v>
+        <v>221</v>
       </c>
       <c r="C19" t="s">
-        <v>217</v>
+        <v>222</v>
       </c>
       <c r="D19" t="s">
-        <v>218</v>
-      </c>
-      <c r="E19">
-        <v>1570</v>
-      </c>
-      <c r="G19" t="s">
-        <v>166</v>
-      </c>
-      <c r="H19">
-        <v>89588429164</v>
-      </c>
-      <c r="I19">
-        <v>2</v>
-      </c>
-      <c r="L19" t="s">
-        <v>20</v>
-      </c>
-      <c r="M19" t="s">
-        <v>21</v>
-      </c>
-      <c r="N19" t="s">
-        <v>22</v>
-      </c>
-      <c r="O19" t="s">
-        <v>219</v>
-      </c>
-    </row>
-    <row r="20" spans="1:15" x14ac:dyDescent="0.3">
+        <v>223</v>
+      </c>
+      <c r="E19" t="s">
+        <v>224</v>
+      </c>
+      <c r="F19" t="s">
+        <v>225</v>
+      </c>
+      <c r="G19">
+        <v>20250729</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A20">
         <v>19</v>
       </c>
       <c r="B20" t="s">
-        <v>220</v>
+        <v>226</v>
       </c>
       <c r="C20" t="s">
-        <v>221</v>
+        <v>227</v>
       </c>
       <c r="D20" t="s">
-        <v>222</v>
-      </c>
-      <c r="E20">
-        <v>1570</v>
-      </c>
-      <c r="G20" t="s">
-        <v>166</v>
-      </c>
-      <c r="H20">
-        <v>89588429161</v>
-      </c>
-      <c r="I20">
-        <v>2</v>
-      </c>
-      <c r="L20" t="s">
-        <v>20</v>
-      </c>
-      <c r="M20" t="s">
-        <v>21</v>
-      </c>
-      <c r="N20" t="s">
-        <v>77</v>
-      </c>
-      <c r="O20" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="21" spans="1:15" x14ac:dyDescent="0.3">
+        <v>228</v>
+      </c>
+      <c r="E20" t="s">
+        <v>229</v>
+      </c>
+      <c r="F20" t="s">
+        <v>230</v>
+      </c>
+      <c r="G20">
+        <v>20250729</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A21">
         <v>20</v>
       </c>
       <c r="B21" t="s">
-        <v>223</v>
+        <v>231</v>
       </c>
       <c r="C21" t="s">
-        <v>224</v>
+        <v>232</v>
       </c>
       <c r="D21" t="s">
-        <v>225</v>
-      </c>
-      <c r="E21">
-        <v>890</v>
-      </c>
-      <c r="G21" t="s">
-        <v>166</v>
-      </c>
-      <c r="H21">
-        <v>89588429167</v>
-      </c>
-      <c r="I21">
-        <v>2</v>
-      </c>
-      <c r="L21" t="s">
-        <v>20</v>
-      </c>
-      <c r="M21" t="s">
-        <v>21</v>
-      </c>
-      <c r="N21" t="s">
-        <v>226</v>
-      </c>
-      <c r="O21" t="s">
-        <v>227</v>
+        <v>233</v>
+      </c>
+      <c r="E21" t="s">
+        <v>234</v>
+      </c>
+      <c r="F21" t="s">
+        <v>235</v>
+      </c>
+      <c r="G21">
+        <v>20250729</v>
       </c>
     </row>
   </sheetData>
@@ -2193,7 +1903,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{40005150-E402-4419-82EA-FA54DF9E346E}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A9BCAEEF-4E94-4567-B04A-000491F803F0}">
   <dimension ref="A1:O21"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <sheetData>
@@ -2245,310 +1955,310 @@
       </c>
     </row>
     <row r="2" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A2">
-        <v>1</v>
+      <c r="A2" t="s">
+        <v>130</v>
       </c>
       <c r="B2" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="C2" t="s">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="D2" t="s">
-        <v>26</v>
+        <v>36</v>
       </c>
       <c r="E2">
-        <v>23920</v>
+        <v>57480</v>
       </c>
       <c r="G2" t="s">
-        <v>19</v>
+        <v>37</v>
       </c>
       <c r="H2">
-        <v>53858743882</v>
+        <v>89588404320</v>
       </c>
       <c r="I2">
         <v>2</v>
       </c>
       <c r="L2" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="M2" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="N2" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="O2" t="s">
-        <v>29</v>
+        <v>38</v>
       </c>
     </row>
     <row r="3" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A3">
-        <v>2</v>
+      <c r="A3" t="s">
+        <v>130</v>
       </c>
       <c r="B3" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="C3" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="D3" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="E3">
-        <v>17020</v>
+        <v>15000</v>
       </c>
       <c r="G3" t="s">
-        <v>19</v>
+        <v>42</v>
       </c>
       <c r="H3">
-        <v>53858734010</v>
+        <v>89588437193</v>
       </c>
       <c r="I3">
         <v>2</v>
       </c>
       <c r="L3" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="M3" t="s">
+        <v>19</v>
+      </c>
+      <c r="N3" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="4" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>130</v>
+      </c>
+      <c r="B4" t="s">
+        <v>43</v>
+      </c>
+      <c r="C4" t="s">
+        <v>44</v>
+      </c>
+      <c r="D4" t="s">
+        <v>45</v>
+      </c>
+      <c r="E4">
+        <v>2130</v>
+      </c>
+      <c r="G4" t="s">
         <v>46</v>
       </c>
-      <c r="N3" t="s">
-        <v>47</v>
-      </c>
-      <c r="O3" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="4" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A4">
-        <v>3</v>
-      </c>
-      <c r="B4" t="s">
-        <v>49</v>
-      </c>
-      <c r="C4" t="s">
-        <v>50</v>
-      </c>
-      <c r="D4" t="s">
-        <v>51</v>
-      </c>
-      <c r="E4">
-        <v>57890</v>
-      </c>
-      <c r="G4" t="s">
-        <v>19</v>
-      </c>
       <c r="H4">
-        <v>53858727893</v>
+        <v>89588314106</v>
       </c>
       <c r="I4">
         <v>2</v>
       </c>
+      <c r="K4" t="s">
+        <v>47</v>
+      </c>
       <c r="L4" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="M4" t="s">
-        <v>52</v>
+        <v>19</v>
       </c>
       <c r="N4" t="s">
-        <v>53</v>
+        <v>22</v>
       </c>
       <c r="O4" t="s">
-        <v>54</v>
+        <v>23</v>
       </c>
     </row>
     <row r="5" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A5">
-        <v>4</v>
+      <c r="A5" t="s">
+        <v>130</v>
       </c>
       <c r="B5" t="s">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="C5" t="s">
-        <v>56</v>
+        <v>49</v>
       </c>
       <c r="D5" t="s">
-        <v>57</v>
+        <v>50</v>
       </c>
       <c r="E5">
-        <v>2970</v>
+        <v>1880</v>
       </c>
       <c r="G5" t="s">
-        <v>58</v>
+        <v>37</v>
       </c>
       <c r="H5">
-        <v>53858722011</v>
+        <v>89588436097</v>
       </c>
       <c r="I5">
         <v>2</v>
       </c>
       <c r="L5" t="s">
-        <v>59</v>
+        <v>18</v>
       </c>
       <c r="M5" t="s">
-        <v>60</v>
+        <v>19</v>
       </c>
       <c r="N5" t="s">
-        <v>61</v>
+        <v>51</v>
       </c>
       <c r="O5" t="s">
-        <v>62</v>
+        <v>52</v>
       </c>
     </row>
     <row r="6" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A6">
-        <v>5</v>
+      <c r="A6" t="s">
+        <v>130</v>
       </c>
       <c r="B6" t="s">
-        <v>63</v>
+        <v>53</v>
       </c>
       <c r="C6" t="s">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="D6" t="s">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="E6">
-        <v>28130</v>
+        <v>5780</v>
       </c>
       <c r="G6" t="s">
-        <v>19</v>
+        <v>56</v>
       </c>
       <c r="H6">
-        <v>53858696356</v>
+        <v>89588435755</v>
       </c>
       <c r="I6">
         <v>2</v>
       </c>
       <c r="L6" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="M6" t="s">
-        <v>46</v>
+        <v>19</v>
       </c>
       <c r="N6" t="s">
-        <v>47</v>
+        <v>57</v>
       </c>
       <c r="O6" t="s">
-        <v>48</v>
+        <v>58</v>
       </c>
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A7">
-        <v>6</v>
+      <c r="A7" t="s">
+        <v>131</v>
       </c>
       <c r="B7" t="s">
-        <v>30</v>
+        <v>59</v>
       </c>
       <c r="C7" t="s">
-        <v>31</v>
+        <v>60</v>
       </c>
       <c r="D7" t="s">
-        <v>32</v>
+        <v>61</v>
       </c>
       <c r="E7">
-        <v>31400</v>
+        <v>2000</v>
       </c>
       <c r="G7" t="s">
-        <v>33</v>
+        <v>62</v>
       </c>
       <c r="H7">
-        <v>89200019767</v>
+        <v>89588305151</v>
       </c>
       <c r="I7">
         <v>2</v>
       </c>
-      <c r="J7" t="s">
-        <v>34</v>
-      </c>
       <c r="K7" t="s">
-        <v>34</v>
+        <v>63</v>
       </c>
       <c r="L7" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="M7" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="N7" t="s">
         <v>22</v>
       </c>
       <c r="O7" t="s">
-        <v>23</v>
+        <v>64</v>
       </c>
     </row>
     <row r="8" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A8">
-        <v>7</v>
+      <c r="A8" t="s">
+        <v>130</v>
       </c>
       <c r="B8" t="s">
-        <v>37</v>
+        <v>65</v>
       </c>
       <c r="C8" t="s">
-        <v>38</v>
+        <v>66</v>
       </c>
       <c r="D8" t="s">
-        <v>39</v>
+        <v>67</v>
       </c>
       <c r="E8">
-        <v>49300</v>
+        <v>8380</v>
       </c>
       <c r="G8" t="s">
-        <v>36</v>
+        <v>68</v>
       </c>
       <c r="H8">
-        <v>89199968681</v>
+        <v>89588433170</v>
       </c>
       <c r="I8">
         <v>2</v>
       </c>
+      <c r="K8" t="s">
+        <v>69</v>
+      </c>
       <c r="L8" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="M8" t="s">
+        <v>19</v>
+      </c>
+      <c r="N8" t="s">
         <v>21</v>
       </c>
-      <c r="N8" t="s">
-        <v>35</v>
-      </c>
     </row>
     <row r="9" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A9">
-        <v>8</v>
+      <c r="A9" t="s">
+        <v>130</v>
       </c>
       <c r="B9" t="s">
-        <v>40</v>
+        <v>70</v>
       </c>
       <c r="C9" t="s">
-        <v>41</v>
+        <v>71</v>
       </c>
       <c r="D9" t="s">
-        <v>42</v>
+        <v>72</v>
       </c>
       <c r="E9">
-        <v>47500</v>
+        <v>51900</v>
       </c>
       <c r="G9" t="s">
-        <v>18</v>
+        <v>37</v>
       </c>
       <c r="H9">
-        <v>53858651732</v>
+        <v>89588433426</v>
       </c>
       <c r="I9">
         <v>2</v>
       </c>
       <c r="L9" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="M9" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="N9" t="s">
-        <v>22</v>
+        <v>73</v>
       </c>
       <c r="O9" t="s">
-        <v>23</v>
+        <v>74</v>
       </c>
     </row>
     <row r="10" spans="1:15" x14ac:dyDescent="0.3">
@@ -2556,37 +2266,37 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>66</v>
+        <v>75</v>
       </c>
       <c r="C10" t="s">
-        <v>67</v>
+        <v>76</v>
       </c>
       <c r="D10" t="s">
-        <v>68</v>
+        <v>77</v>
       </c>
       <c r="E10">
-        <v>17000</v>
+        <v>9900</v>
       </c>
       <c r="G10" t="s">
-        <v>18</v>
+        <v>78</v>
       </c>
       <c r="H10">
-        <v>53858622401</v>
+        <v>89588302111</v>
       </c>
       <c r="I10">
         <v>2</v>
       </c>
       <c r="L10" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="M10" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="N10" t="s">
-        <v>28</v>
+        <v>79</v>
       </c>
       <c r="O10" t="s">
-        <v>29</v>
+        <v>80</v>
       </c>
     </row>
     <row r="11" spans="1:15" x14ac:dyDescent="0.3">
@@ -2594,37 +2304,34 @@
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>69</v>
+        <v>81</v>
       </c>
       <c r="C11" t="s">
-        <v>70</v>
+        <v>82</v>
       </c>
       <c r="D11" t="s">
-        <v>71</v>
+        <v>83</v>
       </c>
       <c r="E11">
-        <v>20430</v>
+        <v>76330</v>
       </c>
       <c r="G11" t="s">
-        <v>72</v>
+        <v>84</v>
       </c>
       <c r="H11">
-        <v>89199897770</v>
+        <v>89588432654</v>
       </c>
       <c r="I11">
         <v>2</v>
       </c>
       <c r="L11" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="M11" t="s">
+        <v>19</v>
+      </c>
+      <c r="N11" t="s">
         <v>21</v>
-      </c>
-      <c r="N11" t="s">
-        <v>22</v>
-      </c>
-      <c r="O11" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="12" spans="1:15" x14ac:dyDescent="0.3">
@@ -2632,37 +2339,34 @@
         <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>73</v>
+        <v>85</v>
       </c>
       <c r="C12" t="s">
-        <v>74</v>
+        <v>86</v>
       </c>
       <c r="D12" t="s">
-        <v>75</v>
+        <v>87</v>
       </c>
       <c r="E12">
-        <v>19300</v>
+        <v>16000</v>
       </c>
       <c r="G12" t="s">
-        <v>76</v>
+        <v>42</v>
       </c>
       <c r="H12">
-        <v>89199841858</v>
+        <v>89588431561</v>
       </c>
       <c r="I12">
         <v>2</v>
       </c>
       <c r="L12" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="M12" t="s">
+        <v>19</v>
+      </c>
+      <c r="N12" t="s">
         <v>21</v>
-      </c>
-      <c r="N12" t="s">
-        <v>77</v>
-      </c>
-      <c r="O12" t="s">
-        <v>78</v>
       </c>
     </row>
     <row r="13" spans="1:15" x14ac:dyDescent="0.3">
@@ -2670,37 +2374,40 @@
         <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="C13" t="s">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="D13" t="s">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="E13">
-        <v>11400</v>
+        <v>16650</v>
       </c>
       <c r="G13" t="s">
-        <v>18</v>
+        <v>91</v>
       </c>
       <c r="H13">
-        <v>53858521678</v>
+        <v>89588431280</v>
       </c>
       <c r="I13">
         <v>2</v>
       </c>
+      <c r="K13" t="s">
+        <v>92</v>
+      </c>
       <c r="L13" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="M13" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="N13" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="O13" t="s">
-        <v>82</v>
+        <v>93</v>
       </c>
     </row>
     <row r="14" spans="1:15" x14ac:dyDescent="0.3">
@@ -2708,37 +2415,34 @@
         <v>13</v>
       </c>
       <c r="B14" t="s">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="C14" t="s">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="D14" t="s">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="E14">
-        <v>79990</v>
+        <v>5500</v>
       </c>
       <c r="G14" t="s">
-        <v>18</v>
+        <v>97</v>
       </c>
       <c r="H14">
-        <v>53858391642</v>
+        <v>89588388722</v>
       </c>
       <c r="I14">
         <v>2</v>
       </c>
       <c r="L14" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="M14" t="s">
+        <v>19</v>
+      </c>
+      <c r="N14" t="s">
         <v>21</v>
-      </c>
-      <c r="N14" t="s">
-        <v>22</v>
-      </c>
-      <c r="O14" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="15" spans="1:15" x14ac:dyDescent="0.3">
@@ -2746,40 +2450,37 @@
         <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>86</v>
+        <v>98</v>
       </c>
       <c r="C15" t="s">
-        <v>87</v>
+        <v>99</v>
       </c>
       <c r="D15" t="s">
-        <v>88</v>
+        <v>100</v>
       </c>
       <c r="E15">
-        <v>28340</v>
+        <v>60120</v>
       </c>
       <c r="G15" t="s">
-        <v>18</v>
+        <v>101</v>
       </c>
       <c r="H15">
-        <v>53858387095</v>
+        <v>89588430610</v>
       </c>
       <c r="I15">
         <v>2</v>
       </c>
-      <c r="K15" t="s">
-        <v>89</v>
-      </c>
       <c r="L15" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="M15" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="N15" t="s">
-        <v>22</v>
+        <v>51</v>
       </c>
       <c r="O15" t="s">
-        <v>23</v>
+        <v>102</v>
       </c>
     </row>
     <row r="16" spans="1:15" x14ac:dyDescent="0.3">
@@ -2787,37 +2488,37 @@
         <v>15</v>
       </c>
       <c r="B16" t="s">
-        <v>90</v>
+        <v>103</v>
       </c>
       <c r="C16" t="s">
-        <v>91</v>
+        <v>104</v>
       </c>
       <c r="D16" t="s">
-        <v>92</v>
+        <v>105</v>
       </c>
       <c r="E16">
-        <v>42670</v>
+        <v>11700</v>
       </c>
       <c r="G16" t="s">
-        <v>18</v>
+        <v>106</v>
       </c>
       <c r="H16">
-        <v>53858324859</v>
+        <v>89588429695</v>
       </c>
       <c r="I16">
         <v>2</v>
       </c>
       <c r="L16" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="M16" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="N16" t="s">
-        <v>28</v>
+        <v>107</v>
       </c>
       <c r="O16" t="s">
-        <v>82</v>
+        <v>108</v>
       </c>
     </row>
     <row r="17" spans="1:15" x14ac:dyDescent="0.3">
@@ -2825,37 +2526,34 @@
         <v>16</v>
       </c>
       <c r="B17" t="s">
-        <v>93</v>
+        <v>109</v>
       </c>
       <c r="C17" t="s">
-        <v>94</v>
+        <v>110</v>
       </c>
       <c r="D17" t="s">
-        <v>95</v>
+        <v>111</v>
       </c>
       <c r="E17">
-        <v>33870</v>
+        <v>237800</v>
       </c>
       <c r="G17" t="s">
-        <v>96</v>
+        <v>112</v>
       </c>
       <c r="H17">
-        <v>53858287681</v>
+        <v>89588429526</v>
       </c>
       <c r="I17">
         <v>2</v>
       </c>
       <c r="L17" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="M17" t="s">
-        <v>97</v>
+        <v>113</v>
       </c>
       <c r="N17" t="s">
-        <v>98</v>
-      </c>
-      <c r="O17" t="s">
-        <v>99</v>
+        <v>114</v>
       </c>
     </row>
     <row r="18" spans="1:15" x14ac:dyDescent="0.3">
@@ -2863,37 +2561,37 @@
         <v>17</v>
       </c>
       <c r="B18" t="s">
-        <v>100</v>
+        <v>115</v>
       </c>
       <c r="C18" t="s">
-        <v>101</v>
+        <v>116</v>
       </c>
       <c r="D18" t="s">
-        <v>102</v>
+        <v>117</v>
       </c>
       <c r="E18">
-        <v>38029</v>
+        <v>1080</v>
       </c>
       <c r="G18" t="s">
-        <v>58</v>
+        <v>68</v>
       </c>
       <c r="H18">
-        <v>53858277897</v>
+        <v>89588429160</v>
       </c>
       <c r="I18">
         <v>2</v>
       </c>
       <c r="L18" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="M18" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="N18" t="s">
-        <v>103</v>
+        <v>22</v>
       </c>
       <c r="O18" t="s">
-        <v>104</v>
+        <v>23</v>
       </c>
     </row>
     <row r="19" spans="1:15" x14ac:dyDescent="0.3">
@@ -2901,37 +2599,37 @@
         <v>18</v>
       </c>
       <c r="B19" t="s">
-        <v>105</v>
+        <v>118</v>
       </c>
       <c r="C19" t="s">
-        <v>106</v>
+        <v>119</v>
       </c>
       <c r="D19" t="s">
-        <v>107</v>
+        <v>120</v>
       </c>
       <c r="E19">
-        <v>11100</v>
+        <v>1570</v>
       </c>
       <c r="G19" t="s">
-        <v>96</v>
+        <v>68</v>
       </c>
       <c r="H19">
-        <v>53858271216</v>
+        <v>89588429164</v>
       </c>
       <c r="I19">
         <v>2</v>
       </c>
       <c r="L19" t="s">
-        <v>59</v>
+        <v>18</v>
       </c>
       <c r="M19" t="s">
-        <v>60</v>
+        <v>19</v>
       </c>
       <c r="N19" t="s">
-        <v>108</v>
+        <v>20</v>
       </c>
       <c r="O19" t="s">
-        <v>109</v>
+        <v>121</v>
       </c>
     </row>
     <row r="20" spans="1:15" x14ac:dyDescent="0.3">
@@ -2939,31 +2637,31 @@
         <v>19</v>
       </c>
       <c r="B20" t="s">
-        <v>110</v>
+        <v>122</v>
       </c>
       <c r="C20" t="s">
-        <v>111</v>
+        <v>123</v>
       </c>
       <c r="D20" t="s">
-        <v>112</v>
+        <v>124</v>
       </c>
       <c r="E20">
-        <v>17150</v>
+        <v>1570</v>
       </c>
       <c r="G20" t="s">
-        <v>113</v>
+        <v>68</v>
       </c>
       <c r="H20">
-        <v>89199782272</v>
+        <v>89588429161</v>
       </c>
       <c r="I20">
         <v>2</v>
       </c>
       <c r="L20" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="M20" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="N20" t="s">
         <v>22</v>
@@ -2977,37 +2675,37 @@
         <v>20</v>
       </c>
       <c r="B21" t="s">
-        <v>114</v>
+        <v>125</v>
       </c>
       <c r="C21" t="s">
-        <v>115</v>
+        <v>126</v>
       </c>
       <c r="D21" t="s">
-        <v>116</v>
+        <v>127</v>
       </c>
       <c r="E21">
-        <v>30010</v>
+        <v>890</v>
       </c>
       <c r="G21" t="s">
-        <v>117</v>
+        <v>68</v>
       </c>
       <c r="H21">
-        <v>89199782212</v>
+        <v>89588429167</v>
       </c>
       <c r="I21">
         <v>2</v>
       </c>
       <c r="L21" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="M21" t="s">
-        <v>46</v>
+        <v>19</v>
       </c>
       <c r="N21" t="s">
-        <v>118</v>
+        <v>128</v>
       </c>
       <c r="O21" t="s">
-        <v>119</v>
+        <v>129</v>
       </c>
     </row>
   </sheetData>
